--- a/src/main/resources/static/template_exel/plats/template_import_plats.xlsx
+++ b/src/main/resources/static/template_exel/plats/template_import_plats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="145">
   <si>
     <t>nom</t>
   </si>
@@ -22,83 +22,437 @@
     <t>prixVente</t>
   </si>
   <si>
-    <t>Camarons au Lait de Coco</t>
-  </si>
-  <si>
-    <t>Plats de Résistance</t>
-  </si>
-  <si>
-    <t>35000.000</t>
-  </si>
-  <si>
-    <t>Riz Nature</t>
-  </si>
-  <si>
-    <t>Entrées / Tapas</t>
-  </si>
-  <si>
-    <t>4000.000</t>
-  </si>
-  <si>
-    <t>Brochettes de Poisson</t>
-  </si>
-  <si>
-    <t>28000.000</t>
-  </si>
-  <si>
-    <t>Salade de Fruits Frais</t>
-  </si>
-  <si>
-    <t>Desserts</t>
-  </si>
-  <si>
-    <t>8500.000</t>
-  </si>
-  <si>
-    <t>Jus de Fruits</t>
-  </si>
-  <si>
-    <t>Boissons</t>
-  </si>
-  <si>
-    <t>3500.000</t>
-  </si>
-  <si>
-    <t>Langouste Grillée</t>
-  </si>
-  <si>
-    <t>55000.000</t>
-  </si>
-  <si>
-    <t>Riz à la Créole</t>
-  </si>
-  <si>
-    <t>6000.000</t>
-  </si>
-  <si>
-    <t>Mousse au Chocolat</t>
-  </si>
-  <si>
-    <t>7500.000</t>
-  </si>
-  <si>
-    <t>Eau Minérale</t>
-  </si>
-  <si>
-    <t>2000.000</t>
-  </si>
-  <si>
-    <t>Sauté de Légumes</t>
-  </si>
-  <si>
-    <t>12000.000</t>
+    <t>Akoho gasy (poulet Fermier à malgache) + accompagnements:Riz  blanc</t>
+  </si>
+  <si>
+    <t>Recettes gasy</t>
+  </si>
+  <si>
+    <t>Aran’Akoho sy atiny (Gésier et foie de poulet) + accompagnements:Riz  blanc</t>
+  </si>
+  <si>
+    <t>Gana ritra (Canard mijoté) + accompagnements:Riz  blanc</t>
+  </si>
+  <si>
+    <t>Aran-gana sy atiny (Gesier et foie de canard) + accompagnements:Riz  blanc</t>
+  </si>
+  <si>
+    <t>Lelen’ omby (Langue de bœuf) + accompagnements:Riz blanc</t>
+  </si>
+  <si>
+    <t>Hena omby ritra(Boeuf mijoté) + accompagnements:Riz  blanc</t>
+  </si>
+  <si>
+    <t>Crabe + accompagnements:Riz  blanc</t>
+  </si>
+  <si>
+    <t>Fruits de mer</t>
+  </si>
+  <si>
+    <t>Crevettes + accompagnements:Riz  blanc</t>
+  </si>
+  <si>
+    <t>Calmar + accompagnements:Riz  blanc</t>
+  </si>
+  <si>
+    <t>Poisson + accompagnements:Riz  blanc</t>
+  </si>
+  <si>
+    <t>Langouste + accompagnements:Riz  blanc</t>
+  </si>
+  <si>
+    <t>Camaron (Grosses crevettes ) + accompagnements:Riz  blanc</t>
+  </si>
+  <si>
+    <t>Salade de terrine de poulet</t>
+  </si>
+  <si>
+    <t>Salades &amp; entrées froides</t>
+  </si>
+  <si>
+    <t>salade de fruit de mer</t>
+  </si>
+  <si>
+    <t>salade de mais aux crevettes</t>
+  </si>
+  <si>
+    <t>salade speciale Mama Tsara</t>
+  </si>
+  <si>
+    <t>Gratin de fruits de mer</t>
+  </si>
+  <si>
+    <t>Entrées chaude</t>
+  </si>
+  <si>
+    <t>Gratin de poulet</t>
+  </si>
+  <si>
+    <t>Gratin de charcuterie</t>
+  </si>
+  <si>
+    <t>Gratin de crevettes</t>
+  </si>
+  <si>
+    <t>crepe a la Mama Tsara</t>
+  </si>
+  <si>
+    <t>croquettes de poulet + Accompagnement aux choix (riz blanc /frites /pommes sautees /legumes sautes)</t>
+  </si>
+  <si>
+    <t>Specialités de poulet</t>
+  </si>
+  <si>
+    <t>cuisse de poulet grillée + Accompagnement aux choix (riz blanc /frites /pommes sautees /legumes sautes)</t>
+  </si>
+  <si>
+    <t>poulet roti  + Accompagnement aux choix (riz blanc /frites /pommes sautees /legumes sautes)</t>
+  </si>
+  <si>
+    <t>poulet saute aux legumes  + Accompagnement aux choix (riz blanc /frites /pommes sautees /legumes sautes)</t>
+  </si>
+  <si>
+    <t>brochettes de poulet + Accompagnement aux choix (riz blanc /frites /pommes sautees /legumes sautes)</t>
+  </si>
+  <si>
+    <t>croquettes de poulet facon cordon bleu + Accompagnement aux choix (riz blanc /frites /pommes sautees /legumes sautes)</t>
+  </si>
+  <si>
+    <t>cuisse de poulet special Mama Tsara + Accompagnement aux choix (riz blanc /frites /pommes sautees /legumes sautes)</t>
+  </si>
+  <si>
+    <t>steak pane + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
+  </si>
+  <si>
+    <t>specialites de viandes</t>
+  </si>
+  <si>
+    <t>steack frit  + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
+  </si>
+  <si>
+    <t>steak sauce au poivre vert + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
+  </si>
+  <si>
+    <t>steak de cheval  + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
+  </si>
+  <si>
+    <t>steak pane facon cordon bleu + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
+  </si>
+  <si>
+    <t>emince de zebu saute  au legumes  + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
+  </si>
+  <si>
+    <t>cote de zebu frite  + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
+  </si>
+  <si>
+    <t>cote de zebu grille  + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
+  </si>
+  <si>
+    <t>Cote de zebu pannee+ Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
+  </si>
+  <si>
+    <t>brochettes de zebu  + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
+  </si>
+  <si>
+    <t>ananas caramelise</t>
+  </si>
+  <si>
+    <t>desserts</t>
+  </si>
+  <si>
+    <t>banane flambee</t>
+  </si>
+  <si>
+    <t>brochettes de fruits de saison</t>
+  </si>
+  <si>
+    <t>glace</t>
+  </si>
+  <si>
+    <t>pizza charcuterie</t>
+  </si>
+  <si>
+    <t>pizza</t>
+  </si>
+  <si>
+    <t>pizza poulet</t>
+  </si>
+  <si>
+    <t>pizza fruits de mers</t>
+  </si>
+  <si>
+    <t>pizza speciale mama tsara</t>
+  </si>
+  <si>
+    <t>soupes de poisson</t>
+  </si>
+  <si>
+    <t>soupes</t>
+  </si>
+  <si>
+    <t>soupes aux fruits de mers</t>
+  </si>
+  <si>
+    <t>soupes aux crevettes</t>
+  </si>
+  <si>
+    <t>soupe Van Tan Mine aux poulet</t>
+  </si>
+  <si>
+    <t>soupe Van Tan Mine garnine speciale</t>
+  </si>
+  <si>
+    <t>soupe speciale Mama Tsara</t>
+  </si>
+  <si>
+    <t>soupe silamangany</t>
+  </si>
+  <si>
+    <t>soupe tongotr’ omby</t>
+  </si>
+  <si>
+    <t>spaghettis au fruits de mer</t>
+  </si>
+  <si>
+    <t>spaghettis</t>
+  </si>
+  <si>
+    <t>Spaghettis aux crevettes</t>
+  </si>
+  <si>
+    <t>Spaghettis a la bolognaise</t>
+  </si>
+  <si>
+    <t>Spaghettis speciale mama tsara</t>
+  </si>
+  <si>
+    <t>Mine Sao au poulet</t>
+  </si>
+  <si>
+    <t>Mine Sao</t>
+  </si>
+  <si>
+    <t>Mine Sao au crevettes</t>
+  </si>
+  <si>
+    <t>Mine Sa0 Fruits de mers</t>
+  </si>
+  <si>
+    <t>Mine Sao speciale Mama Tsara</t>
+  </si>
+  <si>
+    <t>Magret de canard poele a l ananas  + accompagnement aux choix (riz blanc /legumes sautes /frites /pommes sautees /spaghettis /Salade verte )</t>
+  </si>
+  <si>
+    <t>Specialites de canard</t>
+  </si>
+  <si>
+    <t>Magret de canard sauce gingembre miel  + accompagnement aux choix (riz blanc /legumes sautes /frites /pommes sautees /spaghettis /Salade verte )</t>
+  </si>
+  <si>
+    <t>Cuisse de canard poivre vert + accompagnement aux choix (riz blanc /legumes sautes /frites /pommes sautees /spaghettis /Salade verte )</t>
+  </si>
+  <si>
+    <t>Ćuisse de canard aux olives vertes  + accompagnement aux choix (riz blanc /legumes sautes /frites /pommes sautees /spaghettis /Salade verte )</t>
+  </si>
+  <si>
+    <t>Poisson frit  (sur commande)</t>
+  </si>
+  <si>
+    <t>poisson</t>
+  </si>
+  <si>
+    <t>filest de poisson pane</t>
+  </si>
+  <si>
+    <t>filet de poisson sauce au poivre vert</t>
+  </si>
+  <si>
+    <t>brochette de poisson</t>
+  </si>
+  <si>
+    <t>crevettes panees</t>
+  </si>
+  <si>
+    <t>crevettes</t>
+  </si>
+  <si>
+    <t>beignets de crevettes</t>
+  </si>
+  <si>
+    <t>crevettes a la creole</t>
+  </si>
+  <si>
+    <t>brochettes de crevettes</t>
+  </si>
+  <si>
+    <t>crevettes sautes au persil</t>
+  </si>
+  <si>
+    <t>camaron grille</t>
+  </si>
+  <si>
+    <t>camaron</t>
+  </si>
+  <si>
+    <t>camaron saute a l ail</t>
+  </si>
+  <si>
+    <t>calmar panne</t>
+  </si>
+  <si>
+    <t>calmars</t>
+  </si>
+  <si>
+    <t>calmar saute aux legumes</t>
+  </si>
+  <si>
+    <t>calmar grille</t>
+  </si>
+  <si>
+    <t>langouste grille + accompagnement aux choix (riz banc ,legummes sauts ,frites ,pommes sautes ,spaghetis  ,salades vertes )</t>
+  </si>
+  <si>
+    <t>langouste</t>
+  </si>
+  <si>
+    <t>langouste saute a l ‘ ail  + accompagnement aux choix (riz banc ,legummes sauts ,frites ,pommes sautes ,spaghetis  ,salades vertes )</t>
+  </si>
+  <si>
+    <t>cafe</t>
+  </si>
+  <si>
+    <t>boisson chaudes</t>
+  </si>
+  <si>
+    <t>expresso mokabia</t>
+  </si>
+  <si>
+    <t>the</t>
+  </si>
+  <si>
+    <t>cacao</t>
+  </si>
+  <si>
+    <t>jus naturel (fruit de saison )</t>
+  </si>
+  <si>
+    <t>boisson fraiches</t>
+  </si>
+  <si>
+    <t>eau vive 1,5 L</t>
+  </si>
+  <si>
+    <t>Cocal-cola 50 cl</t>
+  </si>
+  <si>
+    <t>Caprice orange</t>
+  </si>
+  <si>
+    <t>Caprice grenadine</t>
+  </si>
+  <si>
+    <t>Caprice bonbon anglais</t>
+  </si>
+  <si>
+    <t>Thb 50 cl</t>
+  </si>
+  <si>
+    <t>bieres</t>
+  </si>
+  <si>
+    <t>Beaufort 33 cl</t>
+  </si>
+  <si>
+    <t>colde blanche</t>
+  </si>
+  <si>
+    <t>red label</t>
+  </si>
+  <si>
+    <t>wihisky</t>
+  </si>
+  <si>
+    <t>Grant’s</t>
+  </si>
+  <si>
+    <t>John Peter Yellow</t>
+  </si>
+  <si>
+    <t>John Peter Green</t>
+  </si>
+  <si>
+    <t>Jack Danil’s</t>
+  </si>
+  <si>
+    <t>Maroparasy rouge</t>
+  </si>
+  <si>
+    <t>vins</t>
+  </si>
+  <si>
+    <t>Cote de Fianarana Rouge</t>
+  </si>
+  <si>
+    <t>Maison Grandet</t>
+  </si>
+  <si>
+    <t>Domaine Olivier Benoit</t>
+  </si>
+  <si>
+    <t>Martinie</t>
+  </si>
+  <si>
+    <t>303 Planteur</t>
+  </si>
+  <si>
+    <t>Rhums &amp; spiritueux</t>
+  </si>
+  <si>
+    <t>GM</t>
+  </si>
+  <si>
+    <t>303 Endemique</t>
+  </si>
+  <si>
+    <t>303 Vanilla</t>
+  </si>
+  <si>
+    <t>303 Avorazana</t>
+  </si>
+  <si>
+    <t>Tropic Punch Coco</t>
+  </si>
+  <si>
+    <t>Demi Djama Freeze</t>
+  </si>
+  <si>
+    <t>Djama Cuve Blanche</t>
+  </si>
+  <si>
+    <t>Djama Manga</t>
+  </si>
+  <si>
+    <t>Djama Club</t>
+  </si>
+  <si>
+    <t>Djama Ambre de Nosy Be 1L</t>
+  </si>
+  <si>
+    <t>Djama Ambre 70</t>
+  </si>
+  <si>
+    <t>Valistoff Citron</t>
+  </si>
+  <si>
+    <t>Valistoff Freiza</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -107,15 +461,9 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
       <color rgb="FF2C3E50"/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <color rgb="FF2C3E50"/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
+      <sz val="8"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -138,13 +486,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -485,7 +830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C120"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
@@ -503,113 +848,1312 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C7" s="1">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C8" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="1">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="B10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="1">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="1">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="B12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="1">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="B13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="1">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="C14" s="1">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="B15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="1">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="B16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="1">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="B17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="C18" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="B19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="B20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>26</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="1">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="1">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="1">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="1">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="1">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="1">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="1">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="1">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="1">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="1">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="1">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="1">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="1">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" s="1">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" s="1">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C41" s="1">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" s="1">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C43" s="1">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C45" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47" s="1">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C50" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C51" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C52" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53" s="1">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C54" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C55" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C56" s="1">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C57" s="1">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C58" s="1">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C59" s="1">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C60" s="1">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C61" s="1">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C62" s="1">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C63" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C64" s="1">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C65" s="1">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C66" s="1">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C67" s="1">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C68" s="1">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C69" s="1">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C70" s="1">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C71" s="1">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C72" s="1">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C73" s="1">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C74" s="1">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C75" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C76" s="1">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C77" s="1">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C78" s="1">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C79" s="1">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C80" s="1">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C81" s="1">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C82" s="1">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C83" s="1">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C84" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C85" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C86" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C87" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C88" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C89" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C90" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C91" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C92" s="1">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C93" s="1">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C94" s="1">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C95" s="1">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C96" s="1">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C97" s="1">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C98" s="1">
+        <v>280000</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C99" s="1">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C100" s="1">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C101" s="1">
+        <v>380000</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C102" s="1">
+        <v>39000</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C103" s="1">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C104" s="1">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C105" s="1">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C106" s="1">
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C107" s="1">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C108" s="1">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C109" s="1">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C110" s="1">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C111" s="1">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C112" s="1">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C113" s="1">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C114" s="1">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C115" s="1">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C116" s="1">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C117" s="1">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C118" s="1">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C119" s="1">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C120" s="1">
+        <v>18000</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/static/template_exel/plats/template_import_plats.xlsx
+++ b/src/main/resources/static/template_exel/plats/template_import_plats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="187">
   <si>
     <t>nom</t>
   </si>
@@ -22,430 +22,556 @@
     <t>prixVente</t>
   </si>
   <si>
+    <t>Aran’Akoho sy atiny (Gésier et foie de poulet) + accompagnements:Riz  blanc</t>
+  </si>
+  <si>
+    <t>Recettes gasy</t>
+  </si>
+  <si>
+    <t>15000.000</t>
+  </si>
+  <si>
+    <t>Aran-gana sy atiny (Gesier et foie de canard) + accompagnements:Riz  blanc</t>
+  </si>
+  <si>
+    <t>Crabe + accompagnements:Riz  blanc</t>
+  </si>
+  <si>
+    <t>Fruits de mer</t>
+  </si>
+  <si>
+    <t>25000.000</t>
+  </si>
+  <si>
+    <t>Crevettes + accompagnements:Riz  blanc</t>
+  </si>
+  <si>
+    <t>20000.000</t>
+  </si>
+  <si>
+    <t>Calmar + accompagnements:Riz  blanc</t>
+  </si>
+  <si>
+    <t>30000.000</t>
+  </si>
+  <si>
+    <t>Langouste + accompagnements:Riz  blanc</t>
+  </si>
+  <si>
+    <t>40000.000</t>
+  </si>
+  <si>
+    <t>Camaron (Grosses crevettes ) + accompagnements:Riz  blanc</t>
+  </si>
+  <si>
+    <t>70000.000</t>
+  </si>
+  <si>
+    <t>salade de mais aux crevettes</t>
+  </si>
+  <si>
+    <t>Salades &amp; entrées froides</t>
+  </si>
+  <si>
+    <t>salade speciale Mama Tsara</t>
+  </si>
+  <si>
+    <t>Gratin de fruits de mer</t>
+  </si>
+  <si>
+    <t>Entrées chaude</t>
+  </si>
+  <si>
+    <t>Gratin de poulet</t>
+  </si>
+  <si>
+    <t>Gratin de charcuterie</t>
+  </si>
+  <si>
+    <t>Gratin de crevettes</t>
+  </si>
+  <si>
+    <t>crepe a la Mama Tsara</t>
+  </si>
+  <si>
+    <t>cuisse de poulet grillée + Accompagnement aux choix (riz blanc /frites /pommes sautees /legumes sautes)</t>
+  </si>
+  <si>
+    <t>Specialités de poulet</t>
+  </si>
+  <si>
+    <t>poulet roti  + Accompagnement aux choix (riz blanc /frites /pommes sautees /legumes sautes)</t>
+  </si>
+  <si>
+    <t>45000.000</t>
+  </si>
+  <si>
+    <t>cote de zebu frite  + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
+  </si>
+  <si>
+    <t>specialites de viandes</t>
+  </si>
+  <si>
+    <t>35000.000</t>
+  </si>
+  <si>
+    <t>cote de zebu grille  + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
+  </si>
+  <si>
+    <t>ananas caramelise</t>
+  </si>
+  <si>
+    <t>desserts</t>
+  </si>
+  <si>
+    <t>banane flambee</t>
+  </si>
+  <si>
+    <t>glace</t>
+  </si>
+  <si>
+    <t>pizza speciale mama tsara</t>
+  </si>
+  <si>
+    <t>pizza</t>
+  </si>
+  <si>
+    <t>soupes de poisson</t>
+  </si>
+  <si>
+    <t>soupes</t>
+  </si>
+  <si>
+    <t>soupe silamangany</t>
+  </si>
+  <si>
+    <t>soupe tongotr’ omby</t>
+  </si>
+  <si>
+    <t>spaghettis au fruits de mer</t>
+  </si>
+  <si>
+    <t>spaghettis</t>
+  </si>
+  <si>
+    <t>24000.000</t>
+  </si>
+  <si>
+    <t>Spaghettis aux crevettes</t>
+  </si>
+  <si>
+    <t>Spaghettis a la bolognaise</t>
+  </si>
+  <si>
+    <t>Spaghettis speciale mama tsara</t>
+  </si>
+  <si>
+    <t>Magret de canard poele a l ananas  + accompagnement aux choix (riz blanc /legumes sautes /frites /pommes sautees /spaghettis /Salade verte )</t>
+  </si>
+  <si>
+    <t>Specialites de canard</t>
+  </si>
+  <si>
+    <t>50000.000</t>
+  </si>
+  <si>
+    <t>Magret de canard sauce gingembre miel  + accompagnement aux choix (riz blanc /legumes sautes /frites /pommes sautees /spaghettis /Salade verte )</t>
+  </si>
+  <si>
+    <t>Cuisse de canard poivre vert + accompagnement aux choix (riz blanc /legumes sautes /frites /pommes sautees /spaghettis /Salade verte )</t>
+  </si>
+  <si>
+    <t>Ćuisse de canard aux olives vertes  + accompagnement aux choix (riz blanc /legumes sautes /frites /pommes sautees /spaghettis /Salade verte )</t>
+  </si>
+  <si>
+    <t>brochette de poisson</t>
+  </si>
+  <si>
+    <t>poisson</t>
+  </si>
+  <si>
+    <t>crevettes panees</t>
+  </si>
+  <si>
+    <t>crevettes</t>
+  </si>
+  <si>
+    <t>beignets de crevettes</t>
+  </si>
+  <si>
+    <t>crevettes a la creole</t>
+  </si>
+  <si>
+    <t>crevettes sautes au persil</t>
+  </si>
+  <si>
+    <t>camaron grille</t>
+  </si>
+  <si>
+    <t>camaron</t>
+  </si>
+  <si>
+    <t>camaron saute a l ail</t>
+  </si>
+  <si>
+    <t>calmar panne</t>
+  </si>
+  <si>
+    <t>calmars</t>
+  </si>
+  <si>
+    <t>calmar saute aux legumes</t>
+  </si>
+  <si>
+    <t>croquettes de poulet + Accompagnement aux choix (riz blanc /frites /pommes sautees /legumes sautes)</t>
+  </si>
+  <si>
+    <t>cuisse de poulet special Mama Tsara + Accompagnement aux choix (riz blanc /frites /pommes sautees /legumes sautes)</t>
+  </si>
+  <si>
+    <t>steak pane + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
+  </si>
+  <si>
+    <t>28000.000</t>
+  </si>
+  <si>
+    <t>steack frit  + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
+  </si>
+  <si>
+    <t>emince de zebu saute  au legumes  + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
+  </si>
+  <si>
+    <t>steak sauce au poivre vert + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
+  </si>
+  <si>
+    <t>32000.000</t>
+  </si>
+  <si>
+    <t>steak pane facon cordon bleu + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
+  </si>
+  <si>
+    <t>Cote de zebu pannee+ Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
+  </si>
+  <si>
+    <t>pizza charcuterie</t>
+  </si>
+  <si>
+    <t>pizza fruits de mers</t>
+  </si>
+  <si>
+    <t>pizza poulet</t>
+  </si>
+  <si>
+    <t>brochettes de fruits de saison</t>
+  </si>
+  <si>
+    <t>brochettes</t>
+  </si>
+  <si>
+    <t>soupes aux fruits de mers</t>
+  </si>
+  <si>
+    <t>soupes aux crevettes</t>
+  </si>
+  <si>
+    <t>soupe Van Tan Mine aux poulet</t>
+  </si>
+  <si>
+    <t>soupe Van Tan Mine garnine speciale</t>
+  </si>
+  <si>
+    <t>soupe speciale Mama Tsara</t>
+  </si>
+  <si>
+    <t>Mine Sao au poulet</t>
+  </si>
+  <si>
+    <t>Mine Sao</t>
+  </si>
+  <si>
+    <t>Mine Sao au crevettes</t>
+  </si>
+  <si>
+    <t>Mine Sa0 Fruits de mers</t>
+  </si>
+  <si>
+    <t>Mine Sao speciale Mama Tsara</t>
+  </si>
+  <si>
     <t>Akoho gasy (poulet Fermier à malgache) + accompagnements:Riz  blanc</t>
   </si>
   <si>
-    <t>Recettes gasy</t>
-  </si>
-  <si>
-    <t>Aran’Akoho sy atiny (Gésier et foie de poulet) + accompagnements:Riz  blanc</t>
-  </si>
-  <si>
     <t>Gana ritra (Canard mijoté) + accompagnements:Riz  blanc</t>
   </si>
   <si>
-    <t>Aran-gana sy atiny (Gesier et foie de canard) + accompagnements:Riz  blanc</t>
-  </si>
-  <si>
-    <t>Lelen’ omby (Langue de bœuf) + accompagnements:Riz blanc</t>
+    <t>Lelan’ omby (Langue de bœuf) + accompagnements:Riz blanc</t>
+  </si>
+  <si>
+    <t>Salade de terrine de poulet</t>
+  </si>
+  <si>
+    <t>22000.000</t>
+  </si>
+  <si>
+    <t>salade de fruit de mer</t>
+  </si>
+  <si>
+    <t>brochettes de crevettes</t>
+  </si>
+  <si>
+    <t>brochettes de poulet + Accompagnement aux choix (riz blanc /frites /pommes sautees /legumes sautes)</t>
+  </si>
+  <si>
+    <t>brochettes de zebu  + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
   </si>
   <si>
     <t>Hena omby ritra(Boeuf mijoté) + accompagnements:Riz  blanc</t>
   </si>
   <si>
-    <t>Crabe + accompagnements:Riz  blanc</t>
-  </si>
-  <si>
-    <t>Fruits de mer</t>
-  </si>
-  <si>
-    <t>Crevettes + accompagnements:Riz  blanc</t>
-  </si>
-  <si>
-    <t>Calmar + accompagnements:Riz  blanc</t>
+    <t>filet de poisson sauce au poivre vert</t>
+  </si>
+  <si>
+    <t>filest de poisson pane</t>
+  </si>
+  <si>
+    <t>Poisson frit  (sur commande)</t>
   </si>
   <si>
     <t>Poisson + accompagnements:Riz  blanc</t>
   </si>
   <si>
-    <t>Langouste + accompagnements:Riz  blanc</t>
-  </si>
-  <si>
-    <t>Camaron (Grosses crevettes ) + accompagnements:Riz  blanc</t>
-  </si>
-  <si>
-    <t>Salade de terrine de poulet</t>
-  </si>
-  <si>
-    <t>Salades &amp; entrées froides</t>
-  </si>
-  <si>
-    <t>salade de fruit de mer</t>
-  </si>
-  <si>
-    <t>salade de mais aux crevettes</t>
-  </si>
-  <si>
-    <t>salade speciale Mama Tsara</t>
-  </si>
-  <si>
-    <t>Gratin de fruits de mer</t>
-  </si>
-  <si>
-    <t>Entrées chaude</t>
-  </si>
-  <si>
-    <t>Gratin de poulet</t>
-  </si>
-  <si>
-    <t>Gratin de charcuterie</t>
-  </si>
-  <si>
-    <t>Gratin de crevettes</t>
-  </si>
-  <si>
-    <t>crepe a la Mama Tsara</t>
-  </si>
-  <si>
-    <t>croquettes de poulet + Accompagnement aux choix (riz blanc /frites /pommes sautees /legumes sautes)</t>
-  </si>
-  <si>
-    <t>Specialités de poulet</t>
-  </si>
-  <si>
-    <t>cuisse de poulet grillée + Accompagnement aux choix (riz blanc /frites /pommes sautees /legumes sautes)</t>
-  </si>
-  <si>
-    <t>poulet roti  + Accompagnement aux choix (riz blanc /frites /pommes sautees /legumes sautes)</t>
+    <t>calmar grille</t>
+  </si>
+  <si>
+    <t>langouste grille + accompagnement aux choix (riz banc ,legummes sauts ,frites ,pommes sautes ,spaghetis  ,salades vertes )</t>
+  </si>
+  <si>
+    <t>langouste</t>
+  </si>
+  <si>
+    <t>langouste saute a l ‘ ail  + accompagnement aux choix (riz banc ,legummes sauts ,frites ,pommes sautes ,spaghetis  ,salades vertes )</t>
+  </si>
+  <si>
+    <t>cafe</t>
+  </si>
+  <si>
+    <t>boisson chaudes</t>
+  </si>
+  <si>
+    <t>3000.000</t>
+  </si>
+  <si>
+    <t>expresso mokabia</t>
+  </si>
+  <si>
+    <t>4000.000</t>
+  </si>
+  <si>
+    <t>the</t>
+  </si>
+  <si>
+    <t>cacao</t>
+  </si>
+  <si>
+    <t>jus naturel (fruit de saison )</t>
+  </si>
+  <si>
+    <t>boisson fraiches</t>
+  </si>
+  <si>
+    <t>5000.000</t>
+  </si>
+  <si>
+    <t>eau vive 1,5 L</t>
+  </si>
+  <si>
+    <t>Cocal-cola 50 cl</t>
+  </si>
+  <si>
+    <t>Caprice orange</t>
+  </si>
+  <si>
+    <t>Caprice grenadine</t>
+  </si>
+  <si>
+    <t>7000.000</t>
+  </si>
+  <si>
+    <t>Caprice bonbon anglais</t>
+  </si>
+  <si>
+    <t>Thb 50 cl</t>
+  </si>
+  <si>
+    <t>bieres</t>
+  </si>
+  <si>
+    <t>8000.000</t>
+  </si>
+  <si>
+    <t>Beaufort 33 cl</t>
+  </si>
+  <si>
+    <t>colde blanche</t>
+  </si>
+  <si>
+    <t>red label</t>
+  </si>
+  <si>
+    <t>wihisky</t>
+  </si>
+  <si>
+    <t>250000.000</t>
+  </si>
+  <si>
+    <t>Grant’s</t>
+  </si>
+  <si>
+    <t>280000.000</t>
+  </si>
+  <si>
+    <t>John Peter Yellow</t>
+  </si>
+  <si>
+    <t>John Peter Green</t>
+  </si>
+  <si>
+    <t>Jack Danil’s</t>
+  </si>
+  <si>
+    <t>380000.000</t>
+  </si>
+  <si>
+    <t>Maroparasy rouge</t>
+  </si>
+  <si>
+    <t>vins</t>
+  </si>
+  <si>
+    <t>39000.000</t>
+  </si>
+  <si>
+    <t>Cote de Fianarana Rouge</t>
+  </si>
+  <si>
+    <t>Maison Grandet</t>
+  </si>
+  <si>
+    <t>Domaine Olivier Benoit</t>
+  </si>
+  <si>
+    <t>Martinie</t>
+  </si>
+  <si>
+    <t>190000.000</t>
+  </si>
+  <si>
+    <t>303 Planteur</t>
+  </si>
+  <si>
+    <t>Rhums &amp; spiritueux</t>
+  </si>
+  <si>
+    <t>GM</t>
+  </si>
+  <si>
+    <t>303 Endemique</t>
+  </si>
+  <si>
+    <t>55000.000</t>
+  </si>
+  <si>
+    <t>303 Vanilla</t>
+  </si>
+  <si>
+    <t>303 Avorazana</t>
+  </si>
+  <si>
+    <t>60000.000</t>
+  </si>
+  <si>
+    <t>Tropic Punch Coco</t>
+  </si>
+  <si>
+    <t>Demi Djama Freeze</t>
+  </si>
+  <si>
+    <t>9000.000</t>
+  </si>
+  <si>
+    <t>Djama Cuve Blanche</t>
+  </si>
+  <si>
+    <t>18000.000</t>
+  </si>
+  <si>
+    <t>Djama Manga</t>
+  </si>
+  <si>
+    <t>Djama Club</t>
+  </si>
+  <si>
+    <t>Djama Ambre de Nosy Be 1L</t>
+  </si>
+  <si>
+    <t>Djama Ambre 70</t>
+  </si>
+  <si>
+    <t>Valistoff Citron</t>
+  </si>
+  <si>
+    <t>Valistoff Freiza</t>
   </si>
   <si>
     <t>poulet saute aux legumes  + Accompagnement aux choix (riz blanc /frites /pommes sautees /legumes sautes)</t>
   </si>
   <si>
-    <t>brochettes de poulet + Accompagnement aux choix (riz blanc /frites /pommes sautees /legumes sautes)</t>
-  </si>
-  <si>
     <t>croquettes de poulet facon cordon bleu + Accompagnement aux choix (riz blanc /frites /pommes sautees /legumes sautes)</t>
   </si>
   <si>
-    <t>cuisse de poulet special Mama Tsara + Accompagnement aux choix (riz blanc /frites /pommes sautees /legumes sautes)</t>
-  </si>
-  <si>
-    <t>steak pane + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
-  </si>
-  <si>
-    <t>specialites de viandes</t>
-  </si>
-  <si>
-    <t>steack frit  + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
-  </si>
-  <si>
-    <t>steak sauce au poivre vert + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
-  </si>
-  <si>
-    <t>steak de cheval  + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
-  </si>
-  <si>
-    <t>steak pane facon cordon bleu + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
-  </si>
-  <si>
-    <t>emince de zebu saute  au legumes  + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
-  </si>
-  <si>
-    <t>cote de zebu frite  + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
-  </si>
-  <si>
-    <t>cote de zebu grille  + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
-  </si>
-  <si>
-    <t>Cote de zebu pannee+ Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
-  </si>
-  <si>
-    <t>brochettes de zebu  + Accompagnement (riz blanc/frite /pommes sautes /legumes sautes)</t>
-  </si>
-  <si>
-    <t>ananas caramelise</t>
-  </si>
-  <si>
-    <t>desserts</t>
-  </si>
-  <si>
-    <t>banane flambee</t>
-  </si>
-  <si>
-    <t>brochettes de fruits de saison</t>
-  </si>
-  <si>
-    <t>glace</t>
-  </si>
-  <si>
-    <t>pizza charcuterie</t>
-  </si>
-  <si>
-    <t>pizza</t>
-  </si>
-  <si>
-    <t>pizza poulet</t>
-  </si>
-  <si>
-    <t>pizza fruits de mers</t>
-  </si>
-  <si>
-    <t>pizza speciale mama tsara</t>
-  </si>
-  <si>
-    <t>soupes de poisson</t>
-  </si>
-  <si>
-    <t>soupes</t>
-  </si>
-  <si>
-    <t>soupes aux fruits de mers</t>
-  </si>
-  <si>
-    <t>soupes aux crevettes</t>
-  </si>
-  <si>
-    <t>soupe Van Tan Mine aux poulet</t>
-  </si>
-  <si>
-    <t>soupe Van Tan Mine garnine speciale</t>
-  </si>
-  <si>
-    <t>soupe speciale Mama Tsara</t>
-  </si>
-  <si>
-    <t>soupe silamangany</t>
-  </si>
-  <si>
-    <t>soupe tongotr’ omby</t>
-  </si>
-  <si>
-    <t>spaghettis au fruits de mer</t>
-  </si>
-  <si>
-    <t>spaghettis</t>
-  </si>
-  <si>
-    <t>Spaghettis aux crevettes</t>
-  </si>
-  <si>
-    <t>Spaghettis a la bolognaise</t>
-  </si>
-  <si>
-    <t>Spaghettis speciale mama tsara</t>
-  </si>
-  <si>
-    <t>Mine Sao au poulet</t>
-  </si>
-  <si>
-    <t>Mine Sao</t>
-  </si>
-  <si>
-    <t>Mine Sao au crevettes</t>
-  </si>
-  <si>
-    <t>Mine Sa0 Fruits de mers</t>
-  </si>
-  <si>
-    <t>Mine Sao speciale Mama Tsara</t>
-  </si>
-  <si>
-    <t>Magret de canard poele a l ananas  + accompagnement aux choix (riz blanc /legumes sautes /frites /pommes sautees /spaghettis /Salade verte )</t>
-  </si>
-  <si>
-    <t>Specialites de canard</t>
-  </si>
-  <si>
-    <t>Magret de canard sauce gingembre miel  + accompagnement aux choix (riz blanc /legumes sautes /frites /pommes sautees /spaghettis /Salade verte )</t>
-  </si>
-  <si>
-    <t>Cuisse de canard poivre vert + accompagnement aux choix (riz blanc /legumes sautes /frites /pommes sautees /spaghettis /Salade verte )</t>
-  </si>
-  <si>
-    <t>Ćuisse de canard aux olives vertes  + accompagnement aux choix (riz blanc /legumes sautes /frites /pommes sautees /spaghettis /Salade verte )</t>
-  </si>
-  <si>
-    <t>Poisson frit  (sur commande)</t>
-  </si>
-  <si>
-    <t>poisson</t>
-  </si>
-  <si>
-    <t>filest de poisson pane</t>
-  </si>
-  <si>
-    <t>filet de poisson sauce au poivre vert</t>
-  </si>
-  <si>
-    <t>brochette de poisson</t>
-  </si>
-  <si>
-    <t>crevettes panees</t>
-  </si>
-  <si>
-    <t>crevettes</t>
-  </si>
-  <si>
-    <t>beignets de crevettes</t>
-  </si>
-  <si>
-    <t>crevettes a la creole</t>
-  </si>
-  <si>
-    <t>brochettes de crevettes</t>
-  </si>
-  <si>
-    <t>crevettes sautes au persil</t>
-  </si>
-  <si>
-    <t>camaron grille</t>
-  </si>
-  <si>
-    <t>camaron</t>
-  </si>
-  <si>
-    <t>camaron saute a l ail</t>
-  </si>
-  <si>
-    <t>calmar panne</t>
-  </si>
-  <si>
-    <t>calmars</t>
-  </si>
-  <si>
-    <t>calmar saute aux legumes</t>
-  </si>
-  <si>
-    <t>calmar grille</t>
-  </si>
-  <si>
-    <t>langouste grille + accompagnement aux choix (riz banc ,legummes sauts ,frites ,pommes sautes ,spaghetis  ,salades vertes )</t>
-  </si>
-  <si>
-    <t>langouste</t>
-  </si>
-  <si>
-    <t>langouste saute a l ‘ ail  + accompagnement aux choix (riz banc ,legummes sauts ,frites ,pommes sautes ,spaghetis  ,salades vertes )</t>
-  </si>
-  <si>
-    <t>cafe</t>
-  </si>
-  <si>
-    <t>boisson chaudes</t>
-  </si>
-  <si>
-    <t>expresso mokabia</t>
-  </si>
-  <si>
-    <t>the</t>
-  </si>
-  <si>
-    <t>cacao</t>
-  </si>
-  <si>
-    <t>jus naturel (fruit de saison )</t>
-  </si>
-  <si>
-    <t>boisson fraiches</t>
-  </si>
-  <si>
-    <t>eau vive 1,5 L</t>
-  </si>
-  <si>
-    <t>Cocal-cola 50 cl</t>
-  </si>
-  <si>
-    <t>Caprice orange</t>
-  </si>
-  <si>
-    <t>Caprice grenadine</t>
-  </si>
-  <si>
-    <t>Caprice bonbon anglais</t>
-  </si>
-  <si>
-    <t>Thb 50 cl</t>
-  </si>
-  <si>
-    <t>bieres</t>
-  </si>
-  <si>
-    <t>Beaufort 33 cl</t>
-  </si>
-  <si>
-    <t>colde blanche</t>
-  </si>
-  <si>
-    <t>red label</t>
-  </si>
-  <si>
-    <t>wihisky</t>
-  </si>
-  <si>
-    <t>Grant’s</t>
-  </si>
-  <si>
-    <t>John Peter Yellow</t>
-  </si>
-  <si>
-    <t>John Peter Green</t>
-  </si>
-  <si>
-    <t>Jack Danil’s</t>
-  </si>
-  <si>
-    <t>Maroparasy rouge</t>
-  </si>
-  <si>
-    <t>vins</t>
-  </si>
-  <si>
-    <t>Cote de Fianarana Rouge</t>
-  </si>
-  <si>
-    <t>Maison Grandet</t>
-  </si>
-  <si>
-    <t>Domaine Olivier Benoit</t>
-  </si>
-  <si>
-    <t>Martinie</t>
-  </si>
-  <si>
-    <t>303 Planteur</t>
-  </si>
-  <si>
-    <t>Rhums &amp; spiritueux</t>
-  </si>
-  <si>
-    <t>GM</t>
-  </si>
-  <si>
-    <t>303 Endemique</t>
-  </si>
-  <si>
-    <t>303 Vanilla</t>
-  </si>
-  <si>
-    <t>303 Avorazana</t>
-  </si>
-  <si>
-    <t>Tropic Punch Coco</t>
-  </si>
-  <si>
-    <t>Demi Djama Freeze</t>
-  </si>
-  <si>
-    <t>Djama Cuve Blanche</t>
-  </si>
-  <si>
-    <t>Djama Manga</t>
-  </si>
-  <si>
-    <t>Djama Club</t>
-  </si>
-  <si>
-    <t>Djama Ambre de Nosy Be 1L</t>
-  </si>
-  <si>
-    <t>Djama Ambre 70</t>
-  </si>
-  <si>
-    <t>Valistoff Citron</t>
-  </si>
-  <si>
-    <t>Valistoff Freiza</t>
+    <t>38000.000</t>
+  </si>
+  <si>
+    <t>Tagliatelle au fruits de mers</t>
+  </si>
+  <si>
+    <t>tagliatelle</t>
+  </si>
+  <si>
+    <t>Tagliatelle aux crevettes</t>
+  </si>
+  <si>
+    <t>Tagliatelle a la bolognaise</t>
+  </si>
+  <si>
+    <t>Tagliatelle speciale Mama tsara</t>
+  </si>
+  <si>
+    <t>salade de fruits</t>
+  </si>
+  <si>
+    <t>10000.000</t>
+  </si>
+  <si>
+    <t>glace simple boule</t>
+  </si>
+  <si>
+    <t>6000.000</t>
+  </si>
+  <si>
+    <t>glace double boules</t>
+  </si>
+  <si>
+    <t>12000.000</t>
+  </si>
+  <si>
+    <t>crepes aux confitures</t>
+  </si>
+  <si>
+    <t>glace triple boules</t>
+  </si>
+  <si>
+    <t>crystal</t>
   </si>
 </sst>
 </file>
@@ -463,7 +589,7 @@
     <font>
       <color rgb="FF2C3E50"/>
       <sz val="8"/>
-      <name val="Arial"/>
+      <name val="Liberation Sans"/>
     </font>
   </fonts>
   <fills count="2">
@@ -489,7 +615,7 @@
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -830,7 +956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C120"/>
+  <dimension ref="A1:C129"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
@@ -854,1306 +980,1405 @@
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1">
-        <v>25000</v>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1">
-        <v>15000</v>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1">
-        <v>25000</v>
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1">
-        <v>15000</v>
+        <v>8</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1">
-        <v>20000</v>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="1">
-        <v>20000</v>
+        <v>8</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="1">
-        <v>25000</v>
+        <v>8</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="C9" s="1">
-        <v>20000</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="1">
-        <v>30000</v>
+        <v>19</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="1">
-        <v>30000</v>
+        <v>22</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="1">
-        <v>40000</v>
+        <v>22</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="1">
-        <v>70000</v>
+        <v>22</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="1">
-        <v>20000</v>
+        <v>22</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="1">
-        <v>20000</v>
+        <v>22</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="1">
-        <v>20000</v>
+        <v>28</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="1">
-        <v>25000</v>
+        <v>28</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="1">
-        <v>25000</v>
+        <v>32</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="1">
-        <v>25000</v>
+        <v>32</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="1">
-        <v>25000</v>
+        <v>36</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="1">
-        <v>25000</v>
+        <v>36</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="1">
-        <v>30000</v>
+        <v>36</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="1">
-        <v>30000</v>
+        <v>40</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="1">
-        <v>30000</v>
+        <v>42</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="1">
-        <v>45000</v>
+        <v>42</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="1">
-        <v>30000</v>
+        <v>42</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27" s="1">
-        <v>35000</v>
+        <v>46</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" s="1">
-        <v>35000</v>
+        <v>46</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C29" s="1">
-        <v>35000</v>
+        <v>46</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="1">
-        <v>25000</v>
+        <v>46</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="1">
-        <v>25000</v>
+        <v>52</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" s="1">
-        <v>30000</v>
+        <v>52</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="1">
-        <v>30000</v>
+        <v>52</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C34" s="1">
-        <v>35000</v>
+        <v>52</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C35" s="1">
-        <v>25000</v>
+        <v>58</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C36" s="1">
-        <v>35000</v>
+        <v>60</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C37" s="1">
-        <v>35000</v>
+        <v>60</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C38" s="1">
-        <v>35000</v>
+        <v>60</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C39" s="1">
-        <v>25000</v>
+        <v>60</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C40" s="1">
-        <v>15000</v>
+        <v>65</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C41" s="1">
-        <v>15000</v>
+        <v>65</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C42" s="1">
-        <v>15000</v>
+        <v>68</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C43" s="1">
-        <v>15000</v>
+        <v>68</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C44" s="1">
-        <v>25000</v>
+        <v>28</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C45" s="1">
-        <v>25000</v>
+        <v>28</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C46" s="1">
-        <v>25000</v>
+        <v>32</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C47" s="1">
-        <v>30000</v>
+        <v>32</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C48" s="1">
-        <v>25000</v>
+        <v>32</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C49" s="1">
-        <v>25000</v>
+        <v>32</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C50" s="1">
-        <v>25000</v>
+        <v>32</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C51" s="1">
-        <v>25000</v>
+        <v>32</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C52" s="1">
-        <v>25000</v>
+        <v>40</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53" s="1">
-        <v>30000</v>
+        <v>40</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C54" s="1">
-        <v>25000</v>
+        <v>40</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C55" s="1">
-        <v>25000</v>
+        <v>84</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C56" s="1">
-        <v>24000</v>
+        <v>42</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C57" s="1">
-        <v>24000</v>
+        <v>42</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C58" s="1">
-        <v>24000</v>
+        <v>42</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C59" s="1">
-        <v>24000</v>
+        <v>42</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C60" s="1">
-        <v>23000</v>
+        <v>42</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C61" s="1">
-        <v>23000</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C62" s="1">
-        <v>23000</v>
+        <v>91</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C63" s="1">
-        <v>25000</v>
+        <v>91</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C64" s="1">
-        <v>50000</v>
+        <v>91</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C65" s="1">
-        <v>50000</v>
+        <v>4</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C66" s="1">
-        <v>50000</v>
+        <v>4</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C67" s="1">
-        <v>50000</v>
+        <v>4</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C68" s="1">
-        <v>30000</v>
+        <v>19</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C69" s="1">
-        <v>30000</v>
+        <v>19</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C70" s="1">
-        <v>30000</v>
+      <c r="C70" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C71" s="1">
-        <v>30000</v>
+        <v>84</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C72" s="1">
-        <v>30000</v>
+        <v>84</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C73" s="1">
-        <v>30000</v>
+        <v>4</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C74" s="1">
-        <v>30000</v>
+        <v>4</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C75" s="1">
-        <v>25000</v>
+        <v>4</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C76" s="1">
-        <v>25000</v>
+        <v>4</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C77" s="1">
-        <v>70000</v>
+        <v>4</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C78" s="1">
-        <v>70000</v>
+        <v>68</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C79" s="1">
-        <v>30000</v>
+        <v>111</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C80" s="1">
-        <v>30000</v>
+        <v>111</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C81" s="1">
-        <v>30000</v>
+        <v>114</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C82" s="1">
-        <v>45000</v>
+        <v>114</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C83" s="1">
-        <v>45000</v>
+        <v>114</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C84" s="1">
-        <v>3000</v>
+        <v>114</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C85" s="1">
-        <v>4000</v>
+        <v>121</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C86" s="1">
-        <v>4000</v>
+        <v>121</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C87" s="1">
-        <v>4000</v>
+        <v>121</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C88" s="1">
-        <v>5000</v>
+        <v>121</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C89" s="1">
-        <v>5000</v>
+        <v>121</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C90" s="1">
-        <v>4000</v>
+        <v>121</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C91" s="1">
-        <v>3000</v>
+        <v>130</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C92" s="1">
-        <v>7000</v>
+        <v>130</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C93" s="1">
-        <v>7000</v>
+        <v>130</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C94" s="1">
-        <v>8000</v>
+        <v>135</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C95" s="1">
-        <v>8000</v>
+        <v>135</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C96" s="1">
-        <v>8000</v>
+        <v>135</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C97" s="1">
-        <v>250000</v>
+        <v>135</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C98" s="1">
-        <v>280000</v>
+        <v>135</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C99" s="1">
-        <v>70000</v>
+        <v>144</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C100" s="1">
-        <v>70000</v>
+        <v>144</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C101" s="1">
-        <v>380000</v>
+        <v>144</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C102" s="1">
-        <v>39000</v>
+        <v>144</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C103" s="1">
-        <v>28000</v>
+        <v>144</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C104" s="1">
-        <v>35000</v>
+        <v>152</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C105" s="1">
-        <v>35000</v>
+        <v>152</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C106" s="1">
-        <v>190000</v>
+        <v>152</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C107" s="1">
-        <v>45000</v>
+        <v>152</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C108" s="1">
-        <v>28000</v>
+        <v>152</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C109" s="1">
-        <v>55000</v>
+        <v>152</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C110" s="1">
-        <v>45000</v>
+        <v>152</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C111" s="1">
-        <v>60000</v>
+        <v>152</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C112" s="1">
-        <v>32000</v>
+        <v>152</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C113" s="1">
-        <v>9000</v>
+        <v>152</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C114" s="1">
-        <v>18000</v>
+        <v>152</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C115" s="1">
-        <v>22000</v>
+        <v>152</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C116" s="1">
-        <v>18000</v>
+        <v>152</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C117" s="1">
-        <v>28000</v>
+        <v>152</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C118" s="1">
-        <v>24000</v>
+        <v>28</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C119" s="1">
-        <v>18000</v>
+        <v>28</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C120" s="1">
-        <v>18000</v>
+        <v>174</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
